--- a/worked_example/data/marginals.xlsx
+++ b/worked_example/data/marginals.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://southwestacademichealthscie-my.sharepoint.com/personal/richard_blackwell_healthinnovationsouthwest_com/Documents/Workspace/intersectionality_using_ipf/worked_example/data/marginals/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://southwestacademichealthscie-my.sharepoint.com/personal/richard_blackwell_healthinnovationsouthwest_com/Documents/Workspace/intersectionality_using_ipf/worked_example/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B37A490A-9A7B-422D-8B27-967B276C84A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{B37A490A-9A7B-422D-8B27-967B276C84A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11159917-C888-4B6E-80B6-71F563C90FE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B112431A-A0FB-40D0-A9E4-F835077F77C6}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11235" activeTab="3" xr2:uid="{B112431A-A0FB-40D0-A9E4-F835077F77C6}"/>
   </bookViews>
   <sheets>
     <sheet name="AGE" sheetId="2" r:id="rId1"/>
@@ -42,29 +42,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
-  <si>
-    <t>E00165923 Forches Ave</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>E00165923</t>
   </si>
   <si>
-    <t>E00180270 Landkey</t>
-  </si>
-  <si>
     <t>E00180270</t>
   </si>
   <si>
-    <t>E00101824 Fremington</t>
-  </si>
-  <si>
     <t>E00101824</t>
   </si>
   <si>
-    <t>E00101827 Croyde</t>
-  </si>
-  <si>
     <t>E00101827</t>
   </si>
   <si>
@@ -96,6 +84,21 @@
   </si>
   <si>
     <t>POOR</t>
+  </si>
+  <si>
+    <t>Forches Avenue</t>
+  </si>
+  <si>
+    <t>Lankey</t>
+  </si>
+  <si>
+    <t>Fremington</t>
+  </si>
+  <si>
+    <t>Croyde</t>
+  </si>
+  <si>
+    <t>OA21NM</t>
   </si>
 </sst>
 </file>
@@ -467,270 +470,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989F1296-171D-4906-A7B0-4C59EEE6B950}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
         <v>340</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>33</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>128</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
         <v>208</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>32</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>133</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>270</v>
+      </c>
+      <c r="D4">
+        <v>72</v>
+      </c>
+      <c r="E4">
+        <v>174</v>
+      </c>
+      <c r="F4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B4">
-        <v>270</v>
-      </c>
-      <c r="C4">
-        <v>72</v>
-      </c>
-      <c r="D4">
-        <v>174</v>
-      </c>
-      <c r="E4">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
         <v>329</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>51</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>164</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>114</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F5">
+    <sortCondition ref="A2:A5"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC16C67C-9429-48B1-8F36-C98A20A91B34}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>204</v>
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="D2">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="E2">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>204</v>
+      </c>
+      <c r="D3">
+        <v>113</v>
+      </c>
+      <c r="E3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>268</v>
+      </c>
+      <c r="D4">
+        <v>138</v>
+      </c>
+      <c r="E4">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
         <v>331</v>
       </c>
-      <c r="C3">
+      <c r="D5">
         <v>184</v>
       </c>
-      <c r="D3">
+      <c r="E5">
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>268</v>
-      </c>
-      <c r="C4">
-        <v>138</v>
-      </c>
-      <c r="D4">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>338</v>
-      </c>
-      <c r="C5">
-        <v>184</v>
-      </c>
-      <c r="D5">
-        <v>154</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E5">
+    <sortCondition ref="A2:A5"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FED1EB-5E8B-4E15-A0E2-032C36772A4F}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>338</v>
+      </c>
+      <c r="D2">
+        <v>230</v>
+      </c>
+      <c r="E2">
+        <v>71</v>
+      </c>
+      <c r="F2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>207</v>
+      </c>
+      <c r="D3">
+        <v>177</v>
+      </c>
+      <c r="E3">
+        <v>27</v>
+      </c>
+      <c r="F3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>268</v>
+      </c>
+      <c r="D4">
+        <v>216</v>
+      </c>
+      <c r="E4">
+        <v>32</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="D1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="C5">
+        <v>332</v>
+      </c>
+      <c r="D5">
+        <v>263</v>
+      </c>
+      <c r="E5">
+        <v>52</v>
+      </c>
+      <c r="F5">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2">
-        <v>338</v>
-      </c>
-      <c r="C2">
-        <v>230</v>
-      </c>
-      <c r="D2">
-        <v>71</v>
-      </c>
-      <c r="E2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3">
-        <v>207</v>
-      </c>
-      <c r="C3">
-        <v>177</v>
-      </c>
-      <c r="D3">
-        <v>27</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>268</v>
-      </c>
-      <c r="C4">
-        <v>216</v>
-      </c>
-      <c r="D4">
-        <v>32</v>
-      </c>
-      <c r="E4">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>332</v>
-      </c>
-      <c r="C5">
-        <v>263</v>
-      </c>
-      <c r="D5">
-        <v>52</v>
-      </c>
-      <c r="E5">
-        <v>17</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F5">
+    <sortCondition ref="A2:A5"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -740,8 +797,7 @@
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -749,31 +805,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
